--- a/devices/device_info.xlsx
+++ b/devices/device_info.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1381,7 +1381,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="14:14">
+    <row r="7" spans="1:14">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
       <c r="N7" s="1" t="s">
         <v>24</v>
       </c>
